--- a/04_DESIGN_TABLES/DesignTable_2609.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2609.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,6 +593,36 @@
           <t>2609-08-08-08-FG</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.84</v>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>2609-08-08-08-FG</t>
@@ -600,17 +630,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING; 2026-10-09 (staged): M1@DRIVE: OMi Items row 873 M 1 Size = 1.520; N1_2@DRIVE: OMi Items row 873 M 2 Size = 1.230; N1_3@DRIVE: OMi Items row 873 L 1 Size = 1.230; Y1@HEX: OMi Items row 873 Hex Flat = 1.062; D@BORE: OMi Items row 873 Side 1 ID = 0.391; THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library); THDMAJ_A2@DRIVE: 1/2-14 -&gt; 0.84 (end library); THDMAJ_A3@DRIVE: 1/2-14 -&gt; 0.84 (end library); TAPDRILL2@BORE: end-library tap drill of the -08 pipe port = 0.7 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); TAPDRILL3@BORE: end-library tap drill of the -08 pipe port = 0.7 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | RESOLVED 2026-10-09 (staged): body from OMi Items row 873, ports from the end library (not from its own Brennan file) - ASSUMED (one source)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
